--- a/charter_of_accounts.xlsx
+++ b/charter_of_accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://malomatiaqsc-my.sharepoint.com/personal/khamzeh_malomatia_com/Documents/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9FC6124-807B-45B8-BD48-21F24B51900B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F48AD852-40F1-4562-A88D-1D2AA3771AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{159250EC-D886-44EB-A6D1-2DE54CA46BB9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$96</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +44,7 @@
     <author>tc={CA9DC8C5-3C07-4BE0-ABDD-60AF6B6FD80D}</author>
   </authors>
   <commentList>
-    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{CA9DC8C5-3C07-4BE0-ABDD-60AF6B6FD80D}">
+    <comment ref="B46" authorId="0" shapeId="0" xr:uid="{CA9DC8C5-3C07-4BE0-ABDD-60AF6B6FD80D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="116">
   <si>
     <t>BU</t>
   </si>
@@ -65,6 +65,108 @@
     <t>DU</t>
   </si>
   <si>
+    <t>30 Digital Business Operations</t>
+  </si>
+  <si>
+    <t>300000 Digital Business Operations (SBU chief cost)</t>
+  </si>
+  <si>
+    <t>31 Business Process Services (BPS)</t>
+  </si>
+  <si>
+    <t>310000 Business Process Services (BU leader Cost)</t>
+  </si>
+  <si>
+    <t>311100 DPO.Delivery (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>311101 DPO.Delivery (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>312100 CRM.Delivery (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>312101 CRM.Delivery (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>313100 HRO.Delivery   (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>313101 HRO.Delivery  (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>314100 KPO.Delivery   (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>314101 KPO.Delivery  (Profit Centre  / Cost centre)</t>
+  </si>
+  <si>
+    <t>315101 BPS.Workforce management</t>
+  </si>
+  <si>
+    <t>315102 BPS.Project Transition &amp; Transformation</t>
+  </si>
+  <si>
+    <t>315103 BPS.Customer experience</t>
+  </si>
+  <si>
+    <t>315104 BPS.Technology &amp; Infra Mgmt.</t>
+  </si>
+  <si>
+    <t>315105 BPS.Operations Management support</t>
+  </si>
+  <si>
+    <t>319000 BPS.Pre-Sales</t>
+  </si>
+  <si>
+    <t>32 Contact centre (CC)</t>
+  </si>
+  <si>
+    <t>320000 Contact centre (BU leader Cost)</t>
+  </si>
+  <si>
+    <t>321100 Contact centre.Delivery  (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>321101 Contact centre.Delivery (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>322101 CC.Workforce management</t>
+  </si>
+  <si>
+    <t>322102 CC.Project Transition &amp; Transformation</t>
+  </si>
+  <si>
+    <t>322103 CC.Customer experience</t>
+  </si>
+  <si>
+    <t>322104 CC.Technology &amp; Infra Mgmt.</t>
+  </si>
+  <si>
+    <t>322105 CC.Operations Management support</t>
+  </si>
+  <si>
+    <t>329000 CC.Pre sales</t>
+  </si>
+  <si>
+    <t>33 Capability sales - Digital business operations</t>
+  </si>
+  <si>
+    <t>330000 DBO.Capability sales</t>
+  </si>
+  <si>
+    <t>34 GRC - Digital business operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340000 DBO.GRC </t>
+  </si>
+  <si>
+    <t>35 Business excellence</t>
+  </si>
+  <si>
+    <t>350000 DBO.Business excellence</t>
+  </si>
+  <si>
     <t>40 Digital services</t>
   </si>
   <si>
@@ -189,13 +291,145 @@
   </si>
   <si>
     <t>460000 Strategic Programs (Strategic Program Leader Cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 Cloud Infrastructure &amp; Security Services </t>
+  </si>
+  <si>
+    <t>500000 Cloud Infrastructure &amp; Security Services (SBU chief cost)</t>
+  </si>
+  <si>
+    <t>51 Cloud &amp; Infrastructure services (CIS)</t>
+  </si>
+  <si>
+    <t>510000 Cloud Advisory &amp; Transformation (BU leader Cost)</t>
+  </si>
+  <si>
+    <t>511100 Cloud Advisory &amp; Transformation (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>511101 Cloud Advisory (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>511102 Cloud Implementation &amp; Transformation (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>511103 Cloud Centre of Excellence (CCoE)</t>
+  </si>
+  <si>
+    <t>511104 Cloud Platform Management</t>
+  </si>
+  <si>
+    <t>511201 Cloud Solutions.Delivery (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>512100 Cloud &amp; Infrastructure Managed services (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>512101 Managed Cloud Services (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>512102 Managed Infrastructure Services (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>512103 Managed Services Desk (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>512104 Managed Monitoring (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>512105 CIMS - Operations support</t>
+  </si>
+  <si>
+    <t>513101 Staff Augmentation.Delivery (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>513100  Staff Augmentation.Delivery  (Practice leader cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">513102 Staff Aug - Operations support </t>
+  </si>
+  <si>
+    <t>519000 CIS.Pre Sales</t>
+  </si>
+  <si>
+    <t>52 Cybersecurity</t>
+  </si>
+  <si>
+    <t>520000 Cybersecurity (BU leader Cost)</t>
+  </si>
+  <si>
+    <t>521100 Security Advisory &amp; Implementation (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>521101 Security Advisory (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>521102 Security Implementation (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>522100 Managed Security Services (Practice leader cost)</t>
+  </si>
+  <si>
+    <t>522101 Security Transition &amp; Transformation (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>522102 Security Service Operations (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <t>522103 Security Operations Support</t>
+  </si>
+  <si>
+    <t>522104 Managed Security Service Delivery (Profit Centre / Cost centre)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">522105 Security </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Platform Management</t>
+    </r>
+  </si>
+  <si>
+    <t>529000 Cybersecurity.Pre sales</t>
+  </si>
+  <si>
+    <t>53 Capability sales - Cloud Infrastructure &amp; Security Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">530000 Cloud Infrastructure &amp; Security Services.Capability sales </t>
+  </si>
+  <si>
+    <t>54 MS Strategic Partner Management - Cloud Infrastructure &amp; Security Services</t>
+  </si>
+  <si>
+    <t>540000 MS Strategic Partner Management  - Cloud Infrastructure &amp; Security Services.Delivery</t>
+  </si>
+  <si>
+    <t>55 GRC - Cloud Infrastructure &amp; Security Services</t>
+  </si>
+  <si>
+    <t>550000 Cloud Infrastructure &amp; Security Services.GRC</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -206,6 +440,12 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -265,19 +505,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,7 +848,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B18" dT="2023-05-09T08:27:51.58" personId="{73608724-E1F6-4B70-9D9F-A65BAEB21608}" id="{CA9DC8C5-3C07-4BE0-ABDD-60AF6B6FD80D}">
+  <threadedComment ref="B46" dT="2023-05-09T08:27:51.58" personId="{73608724-E1F6-4B70-9D9F-A65BAEB21608}" id="{CA9DC8C5-3C07-4BE0-ABDD-60AF6B6FD80D}">
     <text>To be activated only on business need</text>
   </threadedComment>
 </ThreadedComments>
@@ -606,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8283AAAF-D86F-46DE-96BC-4DB0EE3777FF}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="62.7109375" bestFit="1" customWidth="1"/>
@@ -641,7 +891,7 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -657,7 +907,7 @@
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -665,7 +915,7 @@
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -673,7 +923,7 @@
       <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -689,7 +939,7 @@
       <c r="A10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -705,53 +955,53 @@
       <c r="A12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>4</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>4</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>4</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>21</v>
@@ -759,15 +1009,15 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>23</v>
@@ -775,7 +1025,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>24</v>
@@ -783,7 +1033,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>25</v>
@@ -791,118 +1041,598 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    <row r="27" spans="1:2">
+      <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="2" t="s">
+      <c r="A28" s="5" t="s">
         <v>32</v>
       </c>
+      <c r="B28" s="5" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>33</v>
+      <c r="A29" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2" t="s">
-        <v>36</v>
+      <c r="A31" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B36" xr:uid="{8283AAAF-D86F-46DE-96BC-4DB0EE3777FF}"/>
+  <autoFilter ref="A1:B96" xr:uid="{8283AAAF-D86F-46DE-96BC-4DB0EE3777FF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
